--- a/data/trans_dic/IP11A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11A_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,27 +654,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>17,51%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,91</t>
+          <t>4,97; 52,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 54,07</t>
+          <t>0,0; 66,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 42,89</t>
+          <t>4,34; 41,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,54 +789,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,32; 13,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 36,69</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 32,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 14,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>4,56; 34,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,99</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,48</t>
+          <t>0,84; 8,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,47</t>
+          <t>2,55; 15,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,27</t>
+          <t>0,0; 21,5</t>
         </is>
       </c>
     </row>
@@ -939,32 +939,32 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,56</t>
+          <t>0,0; 41,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,35</t>
+          <t>0,0; 58,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,29</t>
+          <t>0,0; 31,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,47</t>
+          <t>0,0; 33,36</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 10,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,85; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,72</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,23</t>
+          <t>0,6; 5,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,65</t>
+          <t>0,57; 6,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,58</t>
+          <t>2,23; 13,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,59</t>
+          <t>2,51; 16,81</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,27 +1373,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1441,27 +1441,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>710</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2834</t>
+          <t>626; 6588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>638; 6805</t>
+          <t>0; 2702</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>797; 7135</t>
+          <t>722; 6967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1654,39 +1654,39 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1581</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>488; 4821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>718; 6054</t>
+          <t>0; 2472</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 4481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>480; 5207</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2432</t>
+          <t>752; 5739</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4274</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>485; 4919</t>
+          <t>485; 5124</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1186; 6930</t>
+          <t>1223; 7538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4964</t>
+          <t>0; 5316</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1257</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 3050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 2943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3735</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4477</t>
+          <t>0; 4153</t>
         </is>
       </c>
     </row>
@@ -1992,37 +1992,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2060,49 +2060,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3230</t>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485; 4975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>626; 7305</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>765; 6280</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>481; 4861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>632; 7867</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>778; 6218</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>485; 5099</t>
+          <t>488; 4903</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712; 8323</t>
+          <t>713; 8145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1426; 7423</t>
+          <t>1428; 8407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1024; 7244</t>
+          <t>990; 6628</t>
         </is>
       </c>
     </row>
